--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="489">
   <si>
     <t>Filename</t>
   </si>
@@ -811,664 +811,676 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9913,0.0019,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9820,0.0002,0.0008,0.0097</t>
-  </si>
-  <si>
-    <t>0.0785,0.0001,0.0002,0.9729</t>
+    <t>0.9532,0.0018,0.0185,0.0032</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.9930,0.0003,0.0002,0.0030</t>
+  </si>
+  <si>
+    <t>0.0258,0.0001,0.0009,0.9888</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
     <t>0.9996,0.0002,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9992,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.5520,0.0020,0.5118,0.0003</t>
-  </si>
-  <si>
-    <t>0.2696,0.0052,0.7403,0.0006</t>
-  </si>
-  <si>
-    <t>0.2871,0.0001,0.8766,0.0000</t>
-  </si>
-  <si>
-    <t>0.0237,0.0001,0.9859,0.0001</t>
-  </si>
-  <si>
-    <t>0.8818,0.0003,0.1546,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9990,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0246,0.9756,0.0013,0.0001</t>
+    <t>0.1102,0.0013,0.8887,0.0006</t>
+  </si>
+  <si>
+    <t>0.0136,0.0005,0.9888,0.0001</t>
+  </si>
+  <si>
+    <t>0.5226,0.0003,0.6801,0.0000</t>
+  </si>
+  <si>
+    <t>0.0224,0.0003,0.9833,0.0001</t>
+  </si>
+  <si>
+    <t>0.9775,0.0003,0.0191,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0524,0.9633,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9971,0.0007,0.0011</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.8495,0.0006,0.1534,0.0009</t>
-  </si>
-  <si>
-    <t>0.0414,0.0001,0.9677,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.2662,0.0000,0.9132,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.0005,0.9971,0.0001</t>
-  </si>
-  <si>
-    <t>0.0057,0.0000,0.9964,0.0001</t>
-  </si>
-  <si>
-    <t>0.2839,0.7141,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.9681,0.0254,0.0041,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.9999,0.0008</t>
-  </si>
-  <si>
-    <t>0.0010,0.9976,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.9818,0.0109,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.9921,0.0013,0.0048,0.0001</t>
-  </si>
-  <si>
-    <t>0.4621,0.6120,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9959,0.0729,0.0000</t>
-  </si>
-  <si>
-    <t>0.0203,0.3147,0.3505,0.0013</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0039,0.0070,0.9902,0.0002</t>
-  </si>
-  <si>
-    <t>0.0065,0.0000,0.9913,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0370,0.4639,0.0019,0.7891</t>
-  </si>
-  <si>
-    <t>0.0013,0.9969,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.0004,0.9988,0.0013,0.0000</t>
+    <t>0.4072,0.0004,0.5970,0.0010</t>
+  </si>
+  <si>
+    <t>0.5871,0.0001,0.5447,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0036,0.0004,0.9939,0.0002</t>
+  </si>
+  <si>
+    <t>0.0319,0.0000,0.9877,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0001,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0045,0.0000,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.6514,0.3077,0.0044,0.0000</t>
+  </si>
+  <si>
+    <t>0.7542,0.1509,0.0469,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9998,0.0008</t>
+  </si>
+  <si>
+    <t>0.0032,0.9900,0.0074,0.0000</t>
+  </si>
+  <si>
+    <t>0.9961,0.0016,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9959,0.0009,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0636,0.9380,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9960,0.4609,0.0000</t>
+  </si>
+  <si>
+    <t>0.0114,0.9539,0.0143,0.0005</t>
+  </si>
+  <si>
+    <t>0.0118,0.0003,0.9845,0.0004</t>
+  </si>
+  <si>
+    <t>0.0117,0.0010,0.9772,0.0008</t>
+  </si>
+  <si>
+    <t>0.0057,0.0000,0.9918,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9987,0.0011</t>
+  </si>
+  <si>
+    <t>0.0754,0.2332,0.0031,0.7756</t>
+  </si>
+  <si>
+    <t>0.0012,0.9969,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0065,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0038,0.0007,0.9910,0.0011</t>
+  </si>
+  <si>
+    <t>0.1481,0.0000,0.9387,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.0001,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9998,0.0004</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0011,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0021,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9905,0.9665,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9985,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8354,0.0003,0.2425,0.0001</t>
+  </si>
+  <si>
+    <t>0.4917,0.0015,0.5498,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0017,0.9996,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9939,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9497,0.5763,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.5409,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9890,0.9887,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0039,0.9987</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0087,0.9981</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0011,0.9990</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9939,0.9798,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9929,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9796,0.9552,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9939,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9919,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9473,0.5790,0.0000</t>
+  </si>
+  <si>
+    <t>0.9940,0.0091,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0018,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0016,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.0002,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.8498,0.0012,0.1157,0.0028</t>
+  </si>
+  <si>
+    <t>0.0111,0.0002,0.9927,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9971,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.9980,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7539,0.3062,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.9464,0.0013,0.0376,0.0008</t>
+  </si>
+  <si>
+    <t>0.9481,0.0000,0.0721,0.0001</t>
+  </si>
+  <si>
+    <t>0.2951,0.2098,0.1136,0.0038</t>
+  </si>
+  <si>
+    <t>0.9223,0.0044,0.0451,0.0014</t>
+  </si>
+  <si>
+    <t>0.0005,0.6256,0.0011,0.9753</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9692,0.0000</t>
+  </si>
+  <si>
+    <t>0.4637,0.6049,0.0033,0.0001</t>
+  </si>
+  <si>
+    <t>0.8211,0.2089,0.0040,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9790,0.9948,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8971,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0064,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0076,0.9941,0.0006</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.5674,0.0003,0.4223,0.0009</t>
+  </si>
+  <si>
+    <t>0.4705,0.0000,0.7346,0.0000</t>
+  </si>
+  <si>
+    <t>0.8118,0.0085,0.1587,0.0013</t>
+  </si>
+  <si>
+    <t>0.0980,0.0001,0.0001,0.9744</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9274,0.9918,0.0000</t>
+  </si>
+  <si>
+    <t>0.0128,0.9834,0.0014,0.0014</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0198,0.9855,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9772,0.0000,0.0003,0.0157</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0027,0.9992,0.0005</t>
+  </si>
+  <si>
+    <t>0.9814,0.0000,0.0179,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.1755,0.6628,0.0366,0.0004</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9746,0.0042,0.0081,0.0005</t>
+  </si>
+  <si>
+    <t>0.1201,0.4419,0.0834,0.0022</t>
+  </si>
+  <si>
+    <t>0.9306,0.0018,0.0739,0.0002</t>
+  </si>
+  <si>
+    <t>0.9927,0.0016,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9949,0.0014,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9891,0.0082,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9638,0.0484,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9224,0.1069,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1831,0.0010,0.8342,0.0007</t>
+  </si>
+  <si>
+    <t>0.9939,0.0073,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0002,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9967,0.0020,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9284,0.0337,0.0235,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9942,0.0034,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0048,0.0047,0.9864,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0933,0.9966,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0013,0.9987,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0003,0.0006,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0005,0.9963,0.0006</t>
-  </si>
-  <si>
-    <t>0.0030,0.0000,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9994,0.0004</t>
-  </si>
-  <si>
-    <t>0.9986,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0016,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0052,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9960,0.0033,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9281,0.9795,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0012,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9969,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.9925,0.0035,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9987,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.4826,0.0006,0.6484,0.0001</t>
-  </si>
-  <si>
-    <t>0.0587,0.0009,0.9587,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0018,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9836,0.2610,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.1940,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9938,0.9959,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.0001,0.9994</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.0083,0.9990</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0006,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9856,0.9569,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9499,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9916,0.9896,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9960,0.9935,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9986,0.9176,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9413,0.9835,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0031,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
+    <t>0.0929,0.0051,0.8923,0.0009</t>
+  </si>
+  <si>
+    <t>0.0019,0.0010,0.9962,0.0001</t>
+  </si>
+  <si>
+    <t>0.0220,0.0036,0.9726,0.0002</t>
+  </si>
+  <si>
+    <t>0.4355,0.0033,0.6505,0.0004</t>
+  </si>
+  <si>
+    <t>0.0066,0.1176,0.8839,0.0003</t>
+  </si>
+  <si>
+    <t>0.8619,0.0042,0.1642,0.0003</t>
+  </si>
+  <si>
+    <t>0.8977,0.0011,0.0772,0.0023</t>
+  </si>
+  <si>
+    <t>0.1428,0.0007,0.8506,0.0009</t>
+  </si>
+  <si>
+    <t>0.0032,0.9962,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5924,0.5339,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.8288,0.2783,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0097,0.9865,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.9542,0.0047,0.0148,0.0004</t>
+  </si>
+  <si>
+    <t>0.9616,0.0001,0.0509,0.0001</t>
+  </si>
+  <si>
+    <t>0.9553,0.0008,0.0084,0.0048</t>
+  </si>
+  <si>
+    <t>0.1362,0.0146,0.8325,0.0044</t>
+  </si>
+  <si>
+    <t>0.9388,0.0001,0.0823,0.0002</t>
+  </si>
+  <si>
+    <t>0.0446,0.0010,0.9687,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.0023,0.9938,0.0004</t>
+  </si>
+  <si>
+    <t>0.0077,0.0233,0.9784,0.0005</t>
+  </si>
+  <si>
+    <t>0.0032,0.0002,0.9957,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.4647,0.8537,0.0001</t>
+  </si>
+  <si>
+    <t>0.9898,0.0076,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9965,0.0018,0.0004,0.0001</t>
   </si>
   <si>
     <t>0.9988,0.0006,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9957,0.0030,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9979,0.0014,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0024,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.9988,0.0002</t>
-  </si>
-  <si>
-    <t>0.0052,0.0005,0.9927,0.0002</t>
-  </si>
-  <si>
-    <t>0.9509,0.0013,0.0281,0.0013</t>
-  </si>
-  <si>
-    <t>0.1292,0.0001,0.9157,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.9938,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0038,0.9951,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1904,0.8557,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.8532,0.0056,0.1455,0.0005</t>
-  </si>
-  <si>
-    <t>0.2087,0.0000,0.8337,0.0003</t>
-  </si>
-  <si>
-    <t>0.9816,0.0005,0.0083,0.0002</t>
-  </si>
-  <si>
-    <t>0.8228,0.0062,0.1572,0.0028</t>
-  </si>
-  <si>
-    <t>0.0004,0.8237,0.0027,0.9650</t>
-  </si>
-  <si>
-    <t>0.0003,0.9989,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9947,0.9803,0.0000</t>
-  </si>
-  <si>
-    <t>0.1459,0.8956,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.8092,0.2027,0.0062,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0001,0.0001</t>
+    <t>0.9978,0.0019,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9992,0.0005</t>
+  </si>
+  <si>
+    <t>0.9078,0.0139,0.0325,0.0010</t>
+  </si>
+  <si>
+    <t>0.9472,0.0018,0.0220,0.0016</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.2899,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0004,0.9959,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0002,0.9968,0.0006</t>
+  </si>
+  <si>
+    <t>0.0011,0.0030,0.9956,0.0002</t>
+  </si>
+  <si>
+    <t>0.0348,0.0011,0.9647,0.0003</t>
+  </si>
+  <si>
+    <t>0.9350,0.0003,0.0625,0.0006</t>
+  </si>
+  <si>
+    <t>0.9904,0.0002,0.0045,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0035,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9947,0.0063,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0015,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0011,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9994,0.0002,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.0158,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.7812,0.9977,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0038,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0005,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.5261,0.0004,0.5158,0.0006</t>
-  </si>
-  <si>
-    <t>0.5763,0.0000,0.6273,0.0000</t>
-  </si>
-  <si>
-    <t>0.9854,0.0003,0.0057,0.0003</t>
-  </si>
-  <si>
-    <t>0.0543,0.0001,0.0009,0.9751</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9875,0.6892,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0574,0.9455,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.0257,0.9804,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0000,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.7736,0.0001,0.0010,0.2205</t>
-  </si>
-  <si>
-    <t>0.0003,0.0010,0.9991,0.0010</t>
-  </si>
-  <si>
-    <t>0.9955,0.0000,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.1628,0.4978,0.1133,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9768,0.0053,0.0068,0.0003</t>
-  </si>
-  <si>
-    <t>0.2517,0.0057,0.5783,0.0013</t>
-  </si>
-  <si>
-    <t>0.8646,0.0428,0.0538,0.0002</t>
-  </si>
-  <si>
-    <t>0.9962,0.0005,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0012,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9903,0.0075,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.6417,0.5324,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9772,0.0257,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0676,0.0005,0.9626,0.0003</t>
-  </si>
-  <si>
-    <t>0.9361,0.1062,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0011,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9498,0.0022,0.0344,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0010,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0047,0.9944,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.3001,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0051,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.2000,0.0017,0.8417,0.0003</t>
-  </si>
-  <si>
-    <t>0.0212,0.0001,0.9845,0.0001</t>
-  </si>
-  <si>
-    <t>0.0080,0.0085,0.9785,0.0004</t>
-  </si>
-  <si>
-    <t>0.5247,0.0024,0.5404,0.0003</t>
-  </si>
-  <si>
-    <t>0.3969,0.0337,0.4378,0.0006</t>
-  </si>
-  <si>
-    <t>0.8990,0.0010,0.1541,0.0002</t>
-  </si>
-  <si>
-    <t>0.9737,0.0021,0.0092,0.0005</t>
-  </si>
-  <si>
-    <t>0.8822,0.0005,0.1369,0.0003</t>
-  </si>
-  <si>
-    <t>0.0044,0.9941,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.9978,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9451,0.0903,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.1210,0.9198,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0291,0.9746,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9514,0.0113,0.0085,0.0001</t>
-  </si>
-  <si>
-    <t>0.5227,0.0001,0.5221,0.0004</t>
-  </si>
-  <si>
-    <t>0.9598,0.0024,0.0056,0.0035</t>
-  </si>
-  <si>
-    <t>0.8335,0.0082,0.1158,0.0045</t>
-  </si>
-  <si>
-    <t>0.3960,0.0007,0.6703,0.0007</t>
-  </si>
-  <si>
-    <t>0.0039,0.0008,0.9964,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9985,0.0009</t>
-  </si>
-  <si>
-    <t>0.0087,0.0135,0.9694,0.0010</t>
-  </si>
-  <si>
-    <t>0.0020,0.0005,0.9969,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0607,0.9800,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9718,0.0323,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.9992,0.0006</t>
-  </si>
-  <si>
-    <t>0.0341,0.0202,0.9179,0.0006</t>
-  </si>
-  <si>
-    <t>0.7143,0.0004,0.2842,0.0007</t>
-  </si>
-  <si>
-    <t>0.0205,0.0000,0.9942,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0029,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0191,0.9940,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0036,0.0010,0.9930,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.0011,0.9955,0.0006</t>
-  </si>
-  <si>
-    <t>0.0011,0.0118,0.9920,0.0019</t>
-  </si>
-  <si>
-    <t>0.7021,0.0021,0.3460,0.0006</t>
-  </si>
-  <si>
-    <t>0.9526,0.0002,0.0530,0.0003</t>
-  </si>
-  <si>
-    <t>0.9900,0.0001,0.0046,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0013,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0021,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0012,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0027,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0118,0.0060,0.9722,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0439,0.0021,0.8801,0.0090</t>
-  </si>
-  <si>
-    <t>0.0759,0.0023,0.8754,0.0056</t>
-  </si>
-  <si>
-    <t>0.0131,0.0012,0.9765,0.0038</t>
-  </si>
-  <si>
-    <t>0.9770,0.0001,0.0015,0.0121</t>
-  </si>
-  <si>
-    <t>0.0009,0.0012,0.0000,0.9994</t>
-  </si>
-  <si>
-    <t>0.0094,0.0001,0.0001,0.9975</t>
-  </si>
-  <si>
-    <t>0.9878,0.0006,0.0003,0.0020</t>
+    <t>0.0007,0.0008,0.9979,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0023,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.4346,0.9924,0.0001</t>
+  </si>
+  <si>
+    <t>0.0770,0.0718,0.8087,0.0016</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0094,0.0001,0.9571,0.0051</t>
+  </si>
+  <si>
+    <t>0.0218,0.0002,0.9791,0.0002</t>
+  </si>
+  <si>
+    <t>0.0179,0.0020,0.9696,0.0013</t>
+  </si>
+  <si>
+    <t>0.9797,0.0000,0.0015,0.0092</t>
+  </si>
+  <si>
+    <t>0.0005,0.0010,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0064,0.0000,0.0000,0.9988</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.9970,0.0002,0.0004,0.0002</t>
   </si>
 </sst>
 </file>
@@ -1952,7 +1964,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1966,7 +1978,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1980,7 +1992,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1994,7 +2006,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2008,7 +2020,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2022,7 +2034,7 @@
         <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2036,7 +2048,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2050,7 +2062,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2064,7 +2076,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2078,7 +2090,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2092,7 +2104,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2106,7 +2118,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2120,7 +2132,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2134,7 +2146,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2148,7 +2160,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2159,10 +2171,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2176,7 +2188,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2190,7 +2202,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2204,7 +2216,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2218,7 +2230,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2232,7 +2244,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2246,7 +2258,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2257,10 +2269,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2274,7 +2286,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2288,7 +2300,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2302,7 +2314,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2316,7 +2328,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2330,7 +2342,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2344,7 +2356,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2358,7 +2370,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2369,10 +2381,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2386,7 +2398,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2400,7 +2412,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2414,7 +2426,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2428,7 +2440,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2442,7 +2454,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2456,7 +2468,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2470,7 +2482,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2484,7 +2496,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2498,7 +2510,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2512,7 +2524,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>282</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2526,7 +2538,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2540,7 +2552,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2554,7 +2566,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2568,7 +2580,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2582,7 +2594,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2596,7 +2608,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2610,7 +2622,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2624,7 +2636,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2638,7 +2650,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2652,7 +2664,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2666,7 +2678,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>318</v>
+        <v>269</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2680,7 +2692,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2694,7 +2706,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>269</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2708,7 +2720,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2722,7 +2734,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2736,7 +2748,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2750,7 +2762,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2764,7 +2776,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2778,7 +2790,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2792,7 +2804,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2803,10 +2815,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2820,7 +2832,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2834,7 +2846,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2848,7 +2860,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2859,10 +2871,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2873,10 +2885,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2890,7 +2902,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2904,7 +2916,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2918,7 +2930,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2932,7 +2944,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2946,7 +2958,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2960,7 +2972,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2974,7 +2986,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2988,7 +3000,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3002,7 +3014,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3016,7 +3028,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3030,7 +3042,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3044,7 +3056,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3058,7 +3070,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3072,7 +3084,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3086,7 +3098,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>346</v>
+        <v>270</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3100,7 +3112,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3114,7 +3126,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3128,7 +3140,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3142,7 +3154,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3156,7 +3168,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3170,7 +3182,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3184,7 +3196,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3198,7 +3210,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>353</v>
+        <v>269</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3212,7 +3224,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3226,7 +3238,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3240,7 +3252,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3254,7 +3266,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3268,7 +3280,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>355</v>
+        <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3282,7 +3294,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3352,7 +3364,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>360</v>
+        <v>284</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3366,7 +3378,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>282</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3408,7 +3420,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>282</v>
+        <v>363</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3422,7 +3434,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3433,7 +3445,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
         <v>364</v>
@@ -3461,7 +3473,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
         <v>366</v>
@@ -3534,7 +3546,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>371</v>
+        <v>310</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3548,7 +3560,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3562,7 +3574,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3576,7 +3588,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3590,7 +3602,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3604,7 +3616,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3618,7 +3630,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3632,7 +3644,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3646,7 +3658,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3660,7 +3672,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3674,7 +3686,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>271</v>
+        <v>379</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3688,7 +3700,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3702,7 +3714,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3716,7 +3728,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>270</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3727,7 +3739,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>382</v>
@@ -3797,7 +3809,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
         <v>387</v>
@@ -3870,7 +3882,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>391</v>
+        <v>342</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3884,7 +3896,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>336</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3898,7 +3910,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3912,7 +3924,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3940,7 +3952,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>348</v>
+        <v>395</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3954,7 +3966,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3968,7 +3980,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3982,7 +3994,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3996,7 +4008,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>348</v>
+        <v>399</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4010,7 +4022,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4024,7 +4036,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4038,7 +4050,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4049,10 +4061,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4066,7 +4078,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4080,7 +4092,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4091,10 +4103,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4108,7 +4120,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4122,7 +4134,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4136,7 +4148,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4150,7 +4162,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>271</v>
+        <v>350</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4164,7 +4176,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4178,7 +4190,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>271</v>
+        <v>410</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4192,7 +4204,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4206,7 +4218,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4220,7 +4232,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>410</v>
+        <v>269</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4234,7 +4246,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>411</v>
+        <v>376</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4248,7 +4260,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4259,10 +4271,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4276,7 +4288,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4290,7 +4302,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4304,7 +4316,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4318,7 +4330,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4332,7 +4344,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4346,7 +4358,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4360,7 +4372,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4374,7 +4386,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4388,7 +4400,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4402,7 +4414,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4416,7 +4428,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4430,7 +4442,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4444,7 +4456,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4458,7 +4470,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>426</v>
+        <v>356</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4472,7 +4484,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4486,7 +4498,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4500,7 +4512,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4514,7 +4526,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4528,7 +4540,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4539,10 +4551,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4556,7 +4568,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4570,7 +4582,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4581,10 +4593,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4598,7 +4610,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4612,7 +4624,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4623,10 +4635,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4637,10 +4649,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4654,7 +4666,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4668,7 +4680,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4679,10 +4691,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4696,7 +4708,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4707,10 +4719,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4721,10 +4733,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4738,7 +4750,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4752,7 +4764,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4766,7 +4778,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4780,7 +4792,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4794,7 +4806,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4808,7 +4820,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4822,7 +4834,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>451</v>
+        <v>376</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4892,7 +4904,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>271</v>
+        <v>456</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4906,7 +4918,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4920,7 +4932,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4931,10 +4943,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4948,7 +4960,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4962,7 +4974,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4976,7 +4988,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4990,7 +5002,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5004,7 +5016,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5018,7 +5030,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5032,7 +5044,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>308</v>
+        <v>465</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5046,7 +5058,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5060,7 +5072,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5071,10 +5083,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5088,7 +5100,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5102,7 +5114,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5116,7 +5128,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>469</v>
+        <v>378</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5130,7 +5142,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>354</v>
+        <v>471</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5144,7 +5156,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>346</v>
+        <v>270</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5158,7 +5170,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5172,7 +5184,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>348</v>
+        <v>274</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5186,7 +5198,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5200,7 +5212,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>272</v>
+        <v>474</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5214,7 +5226,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5228,7 +5240,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5242,7 +5254,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5256,7 +5268,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5270,7 +5282,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5284,7 +5296,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5298,7 +5310,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5312,7 +5324,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5326,7 +5338,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5340,7 +5352,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5354,7 +5366,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5368,7 +5380,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5382,7 +5394,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>336</v>
+        <v>487</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5410,7 +5422,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -808,679 +808,679 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9532,0.0018,0.0185,0.0032</t>
-  </si>
-  <si>
-    <t>0.0003,0.0007,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.9930,0.0003,0.0002,0.0030</t>
-  </si>
-  <si>
-    <t>0.0258,0.0001,0.0009,0.9888</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9552,0.0082,0.0144,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.8710,0.0003,0.0064,0.0669</t>
+  </si>
+  <si>
+    <t>0.2486,0.0000,0.0008,0.8571</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9038,0.0072,0.0565,0.0008</t>
+  </si>
+  <si>
+    <t>0.0204,0.0006,0.9865,0.0001</t>
+  </si>
+  <si>
+    <t>0.0434,0.0002,0.9784,0.0000</t>
+  </si>
+  <si>
+    <t>0.1143,0.0027,0.9094,0.0003</t>
+  </si>
+  <si>
+    <t>0.9299,0.0003,0.0759,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9983,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.0082,0.9896,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9982,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0810,0.0006,0.9028,0.0014</t>
+  </si>
+  <si>
+    <t>0.6536,0.0004,0.4672,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0105,0.0003,0.9867,0.0004</t>
+  </si>
+  <si>
+    <t>0.0680,0.0000,0.9765,0.0000</t>
+  </si>
+  <si>
+    <t>0.3282,0.0004,0.6652,0.0013</t>
+  </si>
+  <si>
+    <t>0.0117,0.0000,0.9942,0.0000</t>
+  </si>
+  <si>
+    <t>0.5606,0.4384,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.1318,0.0210,0.7605,0.0015</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9998,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9933,0.0029,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.7754,0.0007,0.2438,0.0006</t>
+  </si>
+  <si>
+    <t>0.2876,0.7842,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9968,0.0615,0.0000</t>
+  </si>
+  <si>
+    <t>0.0078,0.9233,0.0563,0.0011</t>
+  </si>
+  <si>
+    <t>0.0006,0.0004,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0042,0.0062,0.9883,0.0003</t>
+  </si>
+  <si>
+    <t>0.4394,0.0000,0.2945,0.0014</t>
+  </si>
+  <si>
+    <t>0.0014,0.0003,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9992,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0001,0.9960,0.0019</t>
+  </si>
+  <si>
+    <t>0.0181,0.3028,0.0009,0.9309</t>
+  </si>
+  <si>
+    <t>0.0005,0.9987,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.9984,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0066,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0004,0.9959,0.0019</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0012,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9948,0.0051,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0003</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0010,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9661,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9984,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9990,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9650,0.0009,0.0381,0.0001</t>
+  </si>
+  <si>
+    <t>0.0039,0.0004,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0018,0.9999,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9976,0.9790,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9069,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.6743,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9869,0.9838,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0015,0.9993</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0022,0.9995</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.0004,0.9994</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9962,0.9877,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9927,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9943,0.6704,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9680,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8998,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9512,0.9473,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9963,0.0055,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9953,0.0030,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9829,0.0243,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0061,0.0002,0.9944,0.0001</t>
+  </si>
+  <si>
+    <t>0.9132,0.0025,0.0486,0.0027</t>
+  </si>
+  <si>
+    <t>0.4902,0.0001,0.6719,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0053,0.9917,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9992,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2901,0.7719,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.7742,0.0025,0.2273,0.0007</t>
+  </si>
+  <si>
+    <t>0.9170,0.0001,0.1133,0.0001</t>
+  </si>
+  <si>
+    <t>0.7449,0.0078,0.1975,0.0027</t>
+  </si>
+  <si>
+    <t>0.1942,0.0079,0.7754,0.0015</t>
+  </si>
+  <si>
+    <t>0.0015,0.3748,0.0628,0.7123</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9961,0.9446,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.8259,0.2187,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.8236,0.2019,0.0027,0.0003</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1102,0.0013,0.8887,0.0006</t>
-  </si>
-  <si>
-    <t>0.0136,0.0005,0.9888,0.0001</t>
-  </si>
-  <si>
-    <t>0.5226,0.0003,0.6801,0.0000</t>
-  </si>
-  <si>
-    <t>0.0224,0.0003,0.9833,0.0001</t>
-  </si>
-  <si>
-    <t>0.9775,0.0003,0.0191,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0524,0.9633,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.9971,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4072,0.0004,0.5970,0.0010</t>
-  </si>
-  <si>
-    <t>0.5871,0.0001,0.5447,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0036,0.0004,0.9939,0.0002</t>
-  </si>
-  <si>
-    <t>0.0319,0.0000,0.9877,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0045,0.0000,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.6514,0.3077,0.0044,0.0000</t>
-  </si>
-  <si>
-    <t>0.7542,0.1509,0.0469,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9998,0.0008</t>
-  </si>
-  <si>
-    <t>0.0032,0.9900,0.0074,0.0000</t>
-  </si>
-  <si>
-    <t>0.9961,0.0016,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9959,0.0009,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.0636,0.9380,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9960,0.4609,0.0000</t>
-  </si>
-  <si>
-    <t>0.0114,0.9539,0.0143,0.0005</t>
-  </si>
-  <si>
-    <t>0.0118,0.0003,0.9845,0.0004</t>
-  </si>
-  <si>
-    <t>0.0117,0.0010,0.9772,0.0008</t>
-  </si>
-  <si>
-    <t>0.0057,0.0000,0.9918,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9987,0.0011</t>
-  </si>
-  <si>
-    <t>0.0754,0.2332,0.0031,0.7756</t>
-  </si>
-  <si>
-    <t>0.0012,0.9969,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0065,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.0007,0.9910,0.0011</t>
-  </si>
-  <si>
-    <t>0.1481,0.0000,0.9387,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.0001,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0011,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0021,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9905,0.9665,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0010,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9985,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8354,0.0003,0.2425,0.0001</t>
-  </si>
-  <si>
-    <t>0.4917,0.0015,0.5498,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0017,0.9996,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9939,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9497,0.5763,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.5409,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9890,0.9887,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.0039,0.9987</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0087,0.9981</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.0011,0.9990</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9939,0.9798,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9929,0.9977,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9796,0.9552,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9939,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9919,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9473,0.5790,0.0000</t>
-  </si>
-  <si>
-    <t>0.9940,0.0091,0.0001,0.0000</t>
+    <t>0.9985,0.0001,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9983,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0018,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0016,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.0002,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.8498,0.0012,0.1157,0.0028</t>
-  </si>
-  <si>
-    <t>0.0111,0.0002,0.9927,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.9971,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.9980,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.7539,0.3062,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.9464,0.0013,0.0376,0.0008</t>
-  </si>
-  <si>
-    <t>0.9481,0.0000,0.0721,0.0001</t>
-  </si>
-  <si>
-    <t>0.2951,0.2098,0.1136,0.0038</t>
-  </si>
-  <si>
-    <t>0.9223,0.0044,0.0451,0.0014</t>
-  </si>
-  <si>
-    <t>0.0005,0.6256,0.0011,0.9753</t>
-  </si>
-  <si>
-    <t>0.0003,0.9988,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9692,0.0000</t>
-  </si>
-  <si>
-    <t>0.4637,0.6049,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.8211,0.2089,0.0040,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9790,0.9948,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8971,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0064,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0076,0.9941,0.0006</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.5674,0.0003,0.4223,0.0009</t>
-  </si>
-  <si>
-    <t>0.4705,0.0000,0.7346,0.0000</t>
-  </si>
-  <si>
-    <t>0.8118,0.0085,0.1587,0.0013</t>
-  </si>
-  <si>
-    <t>0.0980,0.0001,0.0001,0.9744</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9274,0.9918,0.0000</t>
-  </si>
-  <si>
-    <t>0.0128,0.9834,0.0014,0.0014</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0198,0.9855,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9772,0.0000,0.0003,0.0157</t>
+    <t>0.9976,0.0004,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0542,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.8458,0.9852,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0005,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0203,0.0040,0.9688,0.0006</t>
+  </si>
+  <si>
+    <t>0.2295,0.0001,0.8909,0.0000</t>
+  </si>
+  <si>
+    <t>0.9578,0.0020,0.0194,0.0008</t>
+  </si>
+  <si>
+    <t>0.0145,0.0000,0.0004,0.9938</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9935,0.9761,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0398,0.9574,0.0009,0.0016</t>
+  </si>
+  <si>
+    <t>0.0417,0.9696,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.8508,0.0006,0.0020,0.0872</t>
+  </si>
+  <si>
+    <t>0.0010,0.0018,0.9978,0.0009</t>
+  </si>
+  <si>
+    <t>0.9928,0.0000,0.0054,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0001,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.6311,0.0461,0.1922,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9783,0.0034,0.0069,0.0004</t>
+  </si>
+  <si>
+    <t>0.9538,0.0058,0.0190,0.0005</t>
+  </si>
+  <si>
+    <t>0.9688,0.0047,0.0157,0.0001</t>
+  </si>
+  <si>
+    <t>0.9948,0.0010,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.9996,0.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0003,0.0027,0.9992,0.0005</t>
-  </si>
-  <si>
-    <t>0.9814,0.0000,0.0179,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.1755,0.6628,0.0366,0.0004</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9746,0.0042,0.0081,0.0005</t>
-  </si>
-  <si>
-    <t>0.1201,0.4419,0.0834,0.0022</t>
-  </si>
-  <si>
-    <t>0.9306,0.0018,0.0739,0.0002</t>
-  </si>
-  <si>
-    <t>0.9927,0.0016,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9949,0.0014,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9891,0.0082,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9638,0.0484,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9224,0.1069,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1831,0.0010,0.8342,0.0007</t>
-  </si>
-  <si>
-    <t>0.9939,0.0073,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0002,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9967,0.0020,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9284,0.0337,0.0235,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9942,0.0034,0.0014,0.0001</t>
+    <t>0.9772,0.0208,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.8825,0.1988,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9631,0.0359,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9306,0.0008,0.0605,0.0003</t>
+  </si>
+  <si>
+    <t>0.9961,0.0030,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0036,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9818,0.0008,0.0151,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9932,0.0044,0.0014,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0001,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0048,0.0047,0.9864,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0933,0.9966,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0013,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0929,0.0051,0.8923,0.0009</t>
-  </si>
-  <si>
-    <t>0.0019,0.0010,0.9962,0.0001</t>
-  </si>
-  <si>
-    <t>0.0220,0.0036,0.9726,0.0002</t>
-  </si>
-  <si>
-    <t>0.4355,0.0033,0.6505,0.0004</t>
-  </si>
-  <si>
-    <t>0.0066,0.1176,0.8839,0.0003</t>
-  </si>
-  <si>
-    <t>0.8619,0.0042,0.1642,0.0003</t>
-  </si>
-  <si>
-    <t>0.8977,0.0011,0.0772,0.0023</t>
-  </si>
-  <si>
-    <t>0.1428,0.0007,0.8506,0.0009</t>
-  </si>
-  <si>
-    <t>0.0032,0.9962,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.5924,0.5339,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.8288,0.2783,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0097,0.9865,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.9542,0.0047,0.0148,0.0004</t>
-  </si>
-  <si>
-    <t>0.9616,0.0001,0.0509,0.0001</t>
-  </si>
-  <si>
-    <t>0.9553,0.0008,0.0084,0.0048</t>
-  </si>
-  <si>
-    <t>0.1362,0.0146,0.8325,0.0044</t>
-  </si>
-  <si>
-    <t>0.9388,0.0001,0.0823,0.0002</t>
-  </si>
-  <si>
-    <t>0.0446,0.0010,0.9687,0.0004</t>
-  </si>
-  <si>
-    <t>0.0015,0.0023,0.9938,0.0004</t>
-  </si>
-  <si>
-    <t>0.0077,0.0233,0.9784,0.0005</t>
-  </si>
-  <si>
-    <t>0.0032,0.0002,0.9957,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.4647,0.8537,0.0001</t>
-  </si>
-  <si>
-    <t>0.9898,0.0076,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9988,0.0008,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0018,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0019,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9992,0.0005</t>
-  </si>
-  <si>
-    <t>0.9078,0.0139,0.0325,0.0010</t>
-  </si>
-  <si>
-    <t>0.9472,0.0018,0.0220,0.0016</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.2899,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0005,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.0004,0.9959,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0002,0.9968,0.0006</t>
-  </si>
-  <si>
-    <t>0.0011,0.0030,0.9956,0.0002</t>
-  </si>
-  <si>
-    <t>0.0348,0.0011,0.9647,0.0003</t>
-  </si>
-  <si>
-    <t>0.9350,0.0003,0.0625,0.0006</t>
-  </si>
-  <si>
-    <t>0.9904,0.0002,0.0045,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0035,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9947,0.0063,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0015,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0008,0.9979,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0023,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.4346,0.9924,0.0001</t>
-  </si>
-  <si>
-    <t>0.0770,0.0718,0.8087,0.0016</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0094,0.0001,0.9571,0.0051</t>
-  </si>
-  <si>
-    <t>0.0218,0.0002,0.9791,0.0002</t>
-  </si>
-  <si>
-    <t>0.0179,0.0020,0.9696,0.0013</t>
-  </si>
-  <si>
-    <t>0.9797,0.0000,0.0015,0.0092</t>
-  </si>
-  <si>
-    <t>0.0005,0.0010,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0064,0.0000,0.0000,0.9988</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0002,0.9999</t>
-  </si>
-  <si>
-    <t>0.9970,0.0002,0.0004,0.0002</t>
+    <t>0.0031,0.0110,0.9883,0.0020</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0123,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.2590,0.0020,0.7877,0.0005</t>
+  </si>
+  <si>
+    <t>0.1706,0.0003,0.8819,0.0002</t>
+  </si>
+  <si>
+    <t>0.0087,0.0027,0.9839,0.0003</t>
+  </si>
+  <si>
+    <t>0.5301,0.0124,0.4540,0.0002</t>
+  </si>
+  <si>
+    <t>0.1053,0.1311,0.5374,0.0005</t>
+  </si>
+  <si>
+    <t>0.8831,0.0005,0.2052,0.0001</t>
+  </si>
+  <si>
+    <t>0.9613,0.0011,0.0155,0.0018</t>
+  </si>
+  <si>
+    <t>0.5571,0.0005,0.5644,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.9977,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9987,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7131,0.4208,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.7421,0.3718,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0334,0.9716,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9539,0.0049,0.0213,0.0003</t>
+  </si>
+  <si>
+    <t>0.9375,0.0004,0.0799,0.0003</t>
+  </si>
+  <si>
+    <t>0.9854,0.0004,0.0025,0.0007</t>
+  </si>
+  <si>
+    <t>0.9252,0.0030,0.0463,0.0022</t>
+  </si>
+  <si>
+    <t>0.8704,0.0002,0.1646,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.0029,0.0037,0.9871,0.0004</t>
+  </si>
+  <si>
+    <t>0.0106,0.0696,0.9502,0.0013</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.1244,0.9155,0.0011</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0017,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9906,0.0054,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9979,0.0012,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9959,0.0028,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0207,0.0066,0.9564,0.0013</t>
+  </si>
+  <si>
+    <t>0.9535,0.0010,0.0231,0.0010</t>
+  </si>
+  <si>
+    <t>0.0009,0.0003,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0074,0.0349,0.9512,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0208,0.9890,0.0008</t>
+  </si>
+  <si>
+    <t>0.3725,0.0025,0.5571,0.0028</t>
+  </si>
+  <si>
+    <t>0.7724,0.0003,0.2264,0.0009</t>
+  </si>
+  <si>
+    <t>0.9944,0.0000,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.9933,0.0080,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9917,0.0104,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9933,0.0049,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.0053,0.9908,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.6137,0.9814,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.0024,0.9870,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0004,0.9947,0.0006</t>
+  </si>
+  <si>
+    <t>0.2214,0.0006,0.8133,0.0006</t>
+  </si>
+  <si>
+    <t>0.0013,0.0003,0.9956,0.0014</t>
+  </si>
+  <si>
+    <t>0.9775,0.0000,0.0069,0.0035</t>
+  </si>
+  <si>
+    <t>0.0009,0.0029,0.0000,0.9993</t>
+  </si>
+  <si>
+    <t>0.0701,0.0000,0.0000,0.9898</t>
+  </si>
+  <si>
+    <t>0.9967,0.0002,0.0004,0.0002</t>
   </si>
 </sst>
 </file>
@@ -1866,7 +1866,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1880,7 +1880,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1894,7 +1894,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1908,7 +1908,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1922,7 +1922,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1936,7 +1936,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1964,7 +1964,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1978,7 +1978,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2006,7 +2006,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2020,7 +2020,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2031,10 +2031,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2048,7 +2048,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2062,7 +2062,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2076,7 +2076,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2090,7 +2090,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2104,7 +2104,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2118,7 +2118,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2132,7 +2132,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2146,7 +2146,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2160,7 +2160,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2174,7 +2174,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2185,10 +2185,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2202,7 +2202,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2216,7 +2216,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2230,7 +2230,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2244,7 +2244,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2258,7 +2258,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2272,7 +2272,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2283,10 +2283,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2300,7 +2300,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2314,7 +2314,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2328,7 +2328,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2342,7 +2342,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2356,7 +2356,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2370,7 +2370,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2384,7 +2384,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2398,7 +2398,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2412,7 +2412,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2423,10 +2423,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2440,7 +2440,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2454,7 +2454,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2468,7 +2468,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2482,7 +2482,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2496,7 +2496,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2510,7 +2510,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2524,7 +2524,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>283</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2538,7 +2538,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2552,7 +2552,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2566,7 +2566,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2580,7 +2580,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2594,7 +2594,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2608,7 +2608,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2622,7 +2622,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2636,7 +2636,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2650,7 +2650,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2664,7 +2664,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2678,7 +2678,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>269</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2692,7 +2692,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2706,7 +2706,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2720,7 +2720,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2734,7 +2734,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2748,7 +2748,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2762,7 +2762,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2776,7 +2776,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2790,7 +2790,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2804,7 +2804,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2818,7 +2818,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2832,7 +2832,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2846,7 +2846,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2860,7 +2860,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2874,7 +2874,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2888,7 +2888,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2902,7 +2902,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2916,7 +2916,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2930,7 +2930,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2944,7 +2944,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2958,7 +2958,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2972,7 +2972,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2986,7 +2986,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3000,7 +3000,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3014,7 +3014,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3028,7 +3028,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3042,7 +3042,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3056,7 +3056,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3070,7 +3070,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3084,7 +3084,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>271</v>
+        <v>347</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3098,7 +3098,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3112,7 +3112,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3126,7 +3126,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3140,7 +3140,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3154,7 +3154,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3168,7 +3168,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3182,7 +3182,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>271</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3196,7 +3196,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3210,7 +3210,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3224,7 +3224,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3238,7 +3238,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3252,7 +3252,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>270</v>
+        <v>347</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3266,7 +3266,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3280,7 +3280,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>269</v>
+        <v>354</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3294,7 +3294,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>274</v>
+        <v>347</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3308,7 +3308,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>312</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3322,7 +3322,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3336,7 +3336,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3350,7 +3350,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3364,7 +3364,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3378,7 +3378,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3392,7 +3392,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3406,7 +3406,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3420,7 +3420,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3434,7 +3434,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3445,10 +3445,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3462,7 +3462,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3476,7 +3476,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3490,7 +3490,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3501,10 +3501,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3515,10 +3515,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3532,7 +3532,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3546,7 +3546,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>310</v>
+        <v>370</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3588,7 +3588,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>280</v>
+        <v>373</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3599,10 +3599,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3616,7 +3616,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3630,7 +3630,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3644,7 +3644,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3658,7 +3658,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3672,7 +3672,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3686,7 +3686,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3700,7 +3700,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3714,7 +3714,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3728,7 +3728,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>270</v>
+        <v>380</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3739,10 +3739,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3756,7 +3756,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3770,7 +3770,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3784,7 +3784,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3798,7 +3798,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3809,10 +3809,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3826,7 +3826,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3840,7 +3840,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3854,7 +3854,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3868,7 +3868,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>391</v>
+        <v>336</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3882,7 +3882,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>342</v>
+        <v>392</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3896,7 +3896,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>392</v>
+        <v>336</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3924,7 +3924,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3938,7 +3938,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3952,7 +3952,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>395</v>
+        <v>347</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4008,7 +4008,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>399</v>
+        <v>347</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4022,7 +4022,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4036,7 +4036,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4050,7 +4050,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4061,10 +4061,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4078,7 +4078,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4092,7 +4092,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4106,7 +4106,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4120,7 +4120,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4134,7 +4134,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4148,7 +4148,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>271</v>
+        <v>408</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4162,7 +4162,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4204,7 +4204,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4218,7 +4218,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4232,7 +4232,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>269</v>
+        <v>412</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4246,7 +4246,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4260,7 +4260,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4274,7 +4274,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4288,7 +4288,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4299,10 +4299,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4316,7 +4316,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4330,7 +4330,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4344,7 +4344,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4358,7 +4358,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4372,7 +4372,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4386,7 +4386,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4400,7 +4400,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4414,7 +4414,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4428,7 +4428,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4442,7 +4442,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4456,7 +4456,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4470,7 +4470,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>356</v>
+        <v>309</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4484,7 +4484,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4498,7 +4498,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4512,7 +4512,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4526,7 +4526,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4537,10 +4537,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4554,7 +4554,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4568,7 +4568,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4582,7 +4582,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4593,10 +4593,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D197" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4610,7 +4610,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4624,7 +4624,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4635,10 +4635,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4652,7 +4652,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4666,7 +4666,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4680,7 +4680,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4694,7 +4694,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4708,7 +4708,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4719,10 +4719,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4736,7 +4736,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4750,7 +4750,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4764,7 +4764,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4778,7 +4778,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4792,7 +4792,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4806,7 +4806,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4820,7 +4820,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>270</v>
+        <v>453</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4834,7 +4834,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>376</v>
+        <v>454</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4848,7 +4848,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4862,7 +4862,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>453</v>
+        <v>271</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4876,7 +4876,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4890,7 +4890,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4904,7 +4904,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4918,7 +4918,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>269</v>
+        <v>347</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4932,7 +4932,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4943,10 +4943,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4960,7 +4960,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4974,7 +4974,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4988,7 +4988,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5002,7 +5002,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5016,7 +5016,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5030,7 +5030,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5044,7 +5044,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>465</v>
+        <v>309</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5058,7 +5058,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5072,7 +5072,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5086,7 +5086,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5100,7 +5100,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5114,7 +5114,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5128,7 +5128,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5142,7 +5142,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5156,7 +5156,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5170,7 +5170,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5184,7 +5184,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>274</v>
+        <v>474</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5198,7 +5198,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5212,7 +5212,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5226,7 +5226,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>475</v>
+        <v>349</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5240,7 +5240,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5254,7 +5254,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5265,10 +5265,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D245" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5282,7 +5282,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5296,7 +5296,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5310,7 +5310,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5324,7 +5324,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5338,7 +5338,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5352,7 +5352,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5366,7 +5366,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5380,7 +5380,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5394,7 +5394,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>487</v>
+        <v>336</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5408,7 +5408,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>391</v>
+        <v>336</v>
       </c>
     </row>
     <row r="256" spans="1:4">
